--- a/AAII_Financials/Yearly/MAX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MAX_YR_FIN.xlsx
@@ -971,10 +971,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>179900</v>
+        <v>55800</v>
       </c>
       <c r="E14" s="3">
-        <v>19800</v>
+        <v>9400</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1186,10 +1186,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2200</v>
+        <v>121900</v>
       </c>
       <c r="E20" s="3">
-        <v>-3900</v>
+        <v>6600</v>
       </c>
       <c r="F20" s="3">
         <v>1800</v>
@@ -1231,10 +1231,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>83300</v>
+        <v>-40800</v>
       </c>
       <c r="E21" s="3">
-        <v>64400</v>
+        <v>53900</v>
       </c>
       <c r="F21" s="3">
         <v>-34400</v>
@@ -1726,10 +1726,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2200</v>
+        <v>-121900</v>
       </c>
       <c r="E32" s="3">
-        <v>3900</v>
+        <v>-6600</v>
       </c>
       <c r="F32" s="3">
         <v>-1800</v>
